--- a/ig/main/ValueSet-JDV-J01-XdsAuthorSpecialty-CISIS.xlsx
+++ b/ig/main/ValueSet-JDV-J01-XdsAuthorSpecialty-CISIS.xlsx
@@ -40,7 +40,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260730120000</t>
+    <t>20260928120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T12:00:00+01:00</t>
+    <t>2026-09-28T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1525,31 +1525,31 @@
     <t>G15_60/SI01</t>
   </si>
   <si>
-    <t>Infirmier - Exercice infirmier en pratique avancée pathologies chroniques stabilisées (SI)</t>
+    <t>Infirmier(ère) en pratique avancée Pathologies chroniques stabilisées (SI)</t>
   </si>
   <si>
     <t>G15_60/SI02</t>
   </si>
   <si>
-    <t>Infirmier - Exercice infirmier en pratique avancée oncologie et hémato-oncologie (SI)</t>
+    <t>Infirmier(ère) en pratique avancée Oncologie et hémato-oncologie (SI)</t>
   </si>
   <si>
     <t>G15_60/SI03</t>
   </si>
   <si>
-    <t>Infirmier - Exerc. infirmier pratique avancée maladie rénale chroniq.,dialyse,transp. rénale (SI)</t>
+    <t>Infirmier(ère) en pratique avancée Maladie rénale chronique, dialyse, transplantation rénale (SI)</t>
   </si>
   <si>
     <t>G15_60/SI04</t>
   </si>
   <si>
-    <t>Infirmier - Exercice infirmier en pratique avancée santé mentale (SI)</t>
+    <t>Infirmier(ère) en pratique avancée Psychiatrie et santé mentale (SI)</t>
   </si>
   <si>
     <t>G15_60/SI05</t>
   </si>
   <si>
-    <t>Infirmier - Exercice infirmier en pratique avancée urgences (SI)</t>
+    <t>Infirmier(ère) en pratique avancée Urgences (SI)</t>
   </si>
   <si>
     <t>G15_60/SI06</t>
